--- a/Sample_Invoicess.xlsx
+++ b/Sample_Invoicess.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\InvoiceProcessingAutomation\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CE33854-439D-47C4-BAFD-4736F5D0A18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2318004E-0D8B-40E5-8F47-1C16BA49B479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3312F7B3-FA44-44B8-97B6-3C8FB6B43CF0}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="5928" xr2:uid="{3312F7B3-FA44-44B8-97B6-3C8FB6B43CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,15 +39,6 @@
     <t>Invoice No</t>
   </si>
   <si>
-    <t xml:space="preserve">Vendor Name </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice date </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount </t>
-  </si>
-  <si>
     <t xml:space="preserve">INV101 </t>
   </si>
   <si>
@@ -130,6 +121,15 @@
   </si>
   <si>
     <t>24/06/2026</t>
+  </si>
+  <si>
+    <t>Vendor Name</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Invoice date</t>
   </si>
 </sst>
 </file>
@@ -495,24 +495,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>25000</v>
@@ -520,13 +520,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>18000</v>
@@ -534,13 +534,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>32000</v>
@@ -548,13 +548,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>27500</v>
@@ -562,10 +562,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>15000</v>
@@ -573,24 +573,24 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>21000</v>
@@ -598,13 +598,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>19000</v>
@@ -612,13 +612,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>35000</v>
@@ -626,10 +626,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
